--- a/Results_experiment/exp_1/preds_1111112222222222.xlsx
+++ b/Results_experiment/exp_1/preds_1111112222222222.xlsx
@@ -1596,7 +1596,7 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-0.689030647277832</v>
+        <v>-0.4009541273117065</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D3">
-        <v>1.455046892166138</v>
+        <v>2.114126682281494</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D4">
-        <v>15.44332790374756</v>
+        <v>14.06388378143311</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D5">
-        <v>16.18327140808105</v>
+        <v>15.15291500091553</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D6">
-        <v>-1.830996513366699</v>
+        <v>-1.771950483322144</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D7">
-        <v>5.318389415740967</v>
+        <v>4.951885223388672</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D8">
-        <v>20.04735565185547</v>
+        <v>17.85483360290527</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>20.5</v>
       </c>
       <c r="D9">
-        <v>14.5078296661377</v>
+        <v>12.02944087982178</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D10">
-        <v>6.267340660095215</v>
+        <v>6.415067672729492</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D11">
-        <v>25.77790451049805</v>
+        <v>22.92801475524902</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D12">
-        <v>4.641912460327148</v>
+        <v>4.400923728942871</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D13">
-        <v>2.119440078735352</v>
+        <v>1.646583318710327</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>-4</v>
       </c>
       <c r="D14">
-        <v>-3.197173118591309</v>
+        <v>-2.059435844421387</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D15">
-        <v>0.6459827423095703</v>
+        <v>2.001223564147949</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>2.893187522888184</v>
+        <v>3.949555158615112</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D17">
-        <v>1.147870063781738</v>
+        <v>1.826383590698242</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>11.36982727050781</v>
+        <v>11.44278144836426</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>2.869545936584473</v>
+        <v>0.3718676567077637</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>-0.1292393803596497</v>
+        <v>-0.290752649307251</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D21">
-        <v>3.754383563995361</v>
+        <v>4.5570068359375</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D22">
-        <v>0.5551103353500366</v>
+        <v>-0.03304207324981689</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D23">
-        <v>9.77503776550293</v>
+        <v>10.2414608001709</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D24">
-        <v>0.4348776936531067</v>
+        <v>0.4870995879173279</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>2.408894777297974</v>
+        <v>1.301136016845703</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>37.90000152587891</v>
       </c>
       <c r="D26">
-        <v>27.48281097412109</v>
+        <v>25.96680641174316</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.5</v>
       </c>
       <c r="D27">
-        <v>6.591171264648438</v>
+        <v>5.250809669494629</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D28">
-        <v>6.967493057250977</v>
+        <v>6.523838996887207</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D29">
-        <v>-2.580146312713623</v>
+        <v>-1.740027189254761</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D30">
-        <v>-0.4118115603923798</v>
+        <v>0.1545479297637939</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D31">
-        <v>3.046889781951904</v>
+        <v>3.713835477828979</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D32">
-        <v>0.6777714490890503</v>
+        <v>0.4558207988739014</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>5.5</v>
       </c>
       <c r="D33">
-        <v>2.140488624572754</v>
+        <v>5.273059844970703</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D34">
-        <v>-1.796302795410156</v>
+        <v>-1.993998765945435</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>5.508257389068604</v>
+        <v>5.843152046203613</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D36">
-        <v>-1.047472476959229</v>
+        <v>-1.206656813621521</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D37">
-        <v>-0.6025291681289673</v>
+        <v>0.196629524230957</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D38">
-        <v>0.5449507236480713</v>
+        <v>0.3885072469711304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>0.5</v>
       </c>
       <c r="D39">
-        <v>1.079608917236328</v>
+        <v>1.575007319450378</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D40">
-        <v>2.456403017044067</v>
+        <v>2.415954828262329</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D41">
-        <v>-0.3084411323070526</v>
+        <v>0.1197524070739746</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D42">
-        <v>-5.856799125671387</v>
+        <v>-5.144051551818848</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D43">
-        <v>0.978498101234436</v>
+        <v>1.288658142089844</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>2.916579484939575</v>
+        <v>3.381230115890503</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D45">
-        <v>-2.122787475585938</v>
+        <v>-1.662144422531128</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D46">
-        <v>5.145254611968994</v>
+        <v>4.596105098724365</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D47">
-        <v>2.682126045227051</v>
+        <v>3.094316482543945</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D48">
-        <v>6.621266841888428</v>
+        <v>5.34398365020752</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D49">
-        <v>1.979549169540405</v>
+        <v>1.867377758026123</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D50">
-        <v>6.433763027191162</v>
+        <v>6.664745330810547</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D51">
-        <v>2.567638158798218</v>
+        <v>2.849144220352173</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>-1.560337066650391</v>
+        <v>-0.3185505867004395</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D53">
-        <v>2.957270622253418</v>
+        <v>3.367733955383301</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>-5.5</v>
       </c>
       <c r="D54">
-        <v>-2.237189292907715</v>
+        <v>-3.709367513656616</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D55">
-        <v>1.128958106040955</v>
+        <v>0.3280994296073914</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="D56">
-        <v>22.25118064880371</v>
+        <v>20.07509803771973</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D57">
-        <v>2.820832252502441</v>
+        <v>3.924148321151733</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>2.650245189666748</v>
+        <v>3.25067400932312</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>-3.5</v>
       </c>
       <c r="D59">
-        <v>-1.430667042732239</v>
+        <v>-1.1479811668396</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D60">
-        <v>-1.138297080993652</v>
+        <v>-0.7390002012252808</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <v>1.55405068397522</v>
+        <v>1.567498207092285</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D62">
-        <v>4.430538177490234</v>
+        <v>4.897856712341309</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>9.144620895385742</v>
+        <v>8.309185028076172</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D64">
-        <v>0.004834145307540894</v>
+        <v>0.2577364444732666</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D65">
-        <v>9.836333274841309</v>
+        <v>11.72687721252441</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D66">
-        <v>16.57526016235352</v>
+        <v>15.29087543487549</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D67">
-        <v>4.229761123657227</v>
+        <v>4.09815502166748</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>0.5</v>
       </c>
       <c r="D68">
-        <v>0.7104375958442688</v>
+        <v>1.725384473800659</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D69">
-        <v>11.18482398986816</v>
+        <v>11.23501491546631</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D70">
-        <v>-0.5838081836700439</v>
+        <v>-1.369187593460083</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D71">
-        <v>0.5401344299316406</v>
+        <v>1.044989347457886</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D72">
-        <v>4.741411209106445</v>
+        <v>3.657244920730591</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D73">
-        <v>0.916104793548584</v>
+        <v>1.631832242012024</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D74">
-        <v>4.860553741455078</v>
+        <v>4.933294296264648</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D75">
-        <v>4.896895885467529</v>
+        <v>4.140337944030762</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1.791582942008972</v>
+        <v>0.1350737810134888</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D77">
-        <v>2.334118366241455</v>
+        <v>1.058290004730225</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D78">
-        <v>5.493354320526123</v>
+        <v>5.909547805786133</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>9.5</v>
       </c>
       <c r="D79">
-        <v>5.195678234100342</v>
+        <v>7.295305252075195</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>0.5</v>
       </c>
       <c r="D80">
-        <v>1.455878853797913</v>
+        <v>0.2386445105075836</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D81">
-        <v>4.159030437469482</v>
+        <v>4.14661693572998</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>1.5</v>
       </c>
       <c r="D82">
-        <v>0.04109123349189758</v>
+        <v>0.143515944480896</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D83">
-        <v>0.7198547124862671</v>
+        <v>1.761157751083374</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>-1</v>
       </c>
       <c r="D84">
-        <v>1.500685214996338</v>
+        <v>3.237221002578735</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D85">
-        <v>1.737594842910767</v>
+        <v>2.314584255218506</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>0.5531196594238281</v>
+        <v>-0.05946004390716553</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D87">
-        <v>8.486921310424805</v>
+        <v>7.171055793762207</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D88">
-        <v>1.977392792701721</v>
+        <v>1.196260929107666</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>15</v>
       </c>
       <c r="D89">
-        <v>13.35298728942871</v>
+        <v>12.56371116638184</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D90">
-        <v>6.410809993743896</v>
+        <v>5.892681121826172</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>-14</v>
       </c>
       <c r="D91">
-        <v>-5.37629222869873</v>
+        <v>-12.29006862640381</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>2.944136142730713</v>
+        <v>1.717624187469482</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>7.5</v>
       </c>
       <c r="D93">
-        <v>3.444478273391724</v>
+        <v>3.679760217666626</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D94">
-        <v>0.0844230055809021</v>
+        <v>0.274699866771698</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>-2</v>
       </c>
       <c r="D95">
-        <v>-2.139079093933105</v>
+        <v>-1.137539982795715</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>15.5</v>
       </c>
       <c r="D96">
-        <v>8.165253639221191</v>
+        <v>8.845606803894043</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>-1.684094309806824</v>
+        <v>-1.501135110855103</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D98">
-        <v>15.26601123809814</v>
+        <v>14.24647045135498</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D99">
-        <v>-0.8522062301635742</v>
+        <v>-1.141695976257324</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D100">
-        <v>2.041232585906982</v>
+        <v>2.188913822174072</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D101">
-        <v>-1.411204099655151</v>
+        <v>-1.056540369987488</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D102">
-        <v>0.8301564455032349</v>
+        <v>0.1230952739715576</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D103">
-        <v>7.243407249450684</v>
+        <v>5.334747314453125</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>3.151049375534058</v>
+        <v>1.078238010406494</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D105">
-        <v>6.538881301879883</v>
+        <v>2.931860208511353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D106">
-        <v>-0.3601252138614655</v>
+        <v>-0.2190985679626465</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D107">
-        <v>2.913531303405762</v>
+        <v>3.303724050521851</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>4.939387321472168</v>
+        <v>6.743390083312988</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>-0.6286402940750122</v>
+        <v>-0.1930608153343201</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D110">
-        <v>0.1087427139282227</v>
+        <v>-0.2633674144744873</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D111">
-        <v>-0.09819987416267395</v>
+        <v>0.08617544174194336</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D112">
-        <v>3.89749002456665</v>
+        <v>5.642391204833984</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D113">
-        <v>1.011702060699463</v>
+        <v>1.031640529632568</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D114">
-        <v>3.67818284034729</v>
+        <v>5.879793167114258</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D115">
-        <v>1.96553647518158</v>
+        <v>1.7702796459198</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D116">
-        <v>-0.6740399599075317</v>
+        <v>-0.8551671504974365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>-1.499332070350647</v>
+        <v>-2.985869646072388</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>1.385155320167542</v>
+        <v>2.165317535400391</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D119">
-        <v>-1.164530038833618</v>
+        <v>-0.8171991109848022</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D120">
-        <v>8.886869430541992</v>
+        <v>9.245770454406738</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>2.793233394622803</v>
+        <v>-0.02349174022674561</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>31.39999961853027</v>
       </c>
       <c r="D122">
-        <v>22.66536903381348</v>
+        <v>21.5871753692627</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D123">
-        <v>-1.506240844726562</v>
+        <v>-0.8989721536636353</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D124">
-        <v>1.647479295730591</v>
+        <v>1.630014300346375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D125">
-        <v>-0.1879503428936005</v>
+        <v>-0.08748394250869751</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D126">
-        <v>-0.4896496832370758</v>
+        <v>-0.4349312782287598</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D127">
-        <v>5.160852432250977</v>
+        <v>3.427855014801025</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="D128">
-        <v>0.111937403678894</v>
+        <v>0.03126060962677002</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D129">
-        <v>1.739219665527344</v>
+        <v>0.5458970665931702</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>1.118259429931641</v>
+        <v>2.058253049850464</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D131">
-        <v>0.5231977105140686</v>
+        <v>1.243125677108765</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D132">
-        <v>4.861153602600098</v>
+        <v>4.783816337585449</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.5</v>
       </c>
       <c r="D133">
-        <v>2.490772247314453</v>
+        <v>2.669563293457031</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D134">
-        <v>0.08641622960567474</v>
+        <v>0.3644537031650543</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>3.5</v>
       </c>
       <c r="D135">
-        <v>0.8832283020019531</v>
+        <v>1.722126603126526</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D136">
-        <v>-3.060246229171753</v>
+        <v>-2.475600957870483</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D137">
-        <v>5.298131465911865</v>
+        <v>6.044797897338867</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D138">
-        <v>-0.2148845493793488</v>
+        <v>-0.3451473712921143</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D139">
-        <v>-0.2632386982440948</v>
+        <v>0.3410780429840088</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D140">
-        <v>1.628439545631409</v>
+        <v>0.9011930227279663</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>6</v>
       </c>
       <c r="D141">
-        <v>5.652612686157227</v>
+        <v>6.913191795349121</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D142">
-        <v>-0.1960719525814056</v>
+        <v>-0.04689222574234009</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>0.349870502948761</v>
+        <v>1.925725221633911</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>-3</v>
       </c>
       <c r="D144">
-        <v>-0.6505415439605713</v>
+        <v>0.2689859867095947</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D145">
-        <v>8.121755599975586</v>
+        <v>7.550887107849121</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D146">
-        <v>0.5735586881637573</v>
+        <v>2.000569581985474</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D147">
-        <v>-0.1214281618595123</v>
+        <v>-0.184503436088562</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>3.135274887084961</v>
+        <v>3.602810144424438</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D149">
-        <v>6.501434803009033</v>
+        <v>6.881450653076172</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D150">
-        <v>-0.07697722315788269</v>
+        <v>0.2773898839950562</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D151">
-        <v>7.202471256256104</v>
+        <v>7.235552787780762</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D152">
-        <v>-0.9741318225860596</v>
+        <v>-0.9452548027038574</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D153">
-        <v>7.029962539672852</v>
+        <v>6.778336524963379</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D154">
-        <v>-0.1417228877544403</v>
+        <v>-0.7726142406463623</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D155">
-        <v>-0.2012391984462738</v>
+        <v>-0.4797688722610474</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="D156">
-        <v>1.868101596832275</v>
+        <v>2.184016466140747</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D157">
-        <v>6.99952507019043</v>
+        <v>6.209307670593262</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D158">
-        <v>0.1022955477237701</v>
+        <v>0.7370346784591675</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D159">
-        <v>4.664607048034668</v>
+        <v>4.762412071228027</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>-9</v>
       </c>
       <c r="D160">
-        <v>0.2299384623765945</v>
+        <v>0.4374649524688721</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D161">
-        <v>2.13495397567749</v>
+        <v>2.466755628585815</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D162">
-        <v>-0.04988884925842285</v>
+        <v>0.4103729724884033</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D163">
-        <v>4.50641918182373</v>
+        <v>5.179134368896484</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D164">
-        <v>-1.044586062431335</v>
+        <v>-0.9482847452163696</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>-2</v>
       </c>
       <c r="D165">
-        <v>-0.2962404191493988</v>
+        <v>-0.2324086427688599</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D166">
-        <v>4.508537292480469</v>
+        <v>3.525727987289429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>-4.5</v>
       </c>
       <c r="D167">
-        <v>-1.996597528457642</v>
+        <v>-1.713622808456421</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D168">
-        <v>1.451936721801758</v>
+        <v>2.6329345703125</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.5</v>
       </c>
       <c r="D169">
-        <v>0.2873850464820862</v>
+        <v>1.398325085639954</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>-0.6718031167984009</v>
+        <v>-0.8226312398910522</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D171">
-        <v>0.7027690410614014</v>
+        <v>0.6749076843261719</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D172">
-        <v>5.213576316833496</v>
+        <v>4.453963279724121</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D173">
-        <v>-1.803420543670654</v>
+        <v>-1.177838563919067</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D174">
-        <v>4.963432312011719</v>
+        <v>4.868799209594727</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="D175">
-        <v>1.815643429756165</v>
+        <v>1.12426483631134</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D176">
-        <v>-2.876594543457031</v>
+        <v>-2.360445737838745</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>-3</v>
       </c>
       <c r="D177">
-        <v>-2.904135704040527</v>
+        <v>-1.480194330215454</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D178">
-        <v>5.939725875854492</v>
+        <v>5.493958473205566</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>28.39999961853027</v>
       </c>
       <c r="D179">
-        <v>15.70132446289062</v>
+        <v>14.20975971221924</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="D180">
-        <v>2.974212646484375</v>
+        <v>0.8498732447624207</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D181">
-        <v>6.785849571228027</v>
+        <v>6.536273956298828</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D182">
-        <v>-2.297041177749634</v>
+        <v>-3.156049013137817</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D183">
-        <v>-3.687854766845703</v>
+        <v>-2.490870475769043</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>8</v>
       </c>
       <c r="D184">
-        <v>5.485993385314941</v>
+        <v>5.716870307922363</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D185">
-        <v>0.8505904674530029</v>
+        <v>1.832049608230591</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D186">
-        <v>2.937882423400879</v>
+        <v>4.16390323638916</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>-3</v>
       </c>
       <c r="D187">
-        <v>0.3014574646949768</v>
+        <v>1.409653663635254</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D188">
-        <v>-0.1505326926708221</v>
+        <v>0.5091969966888428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D189">
-        <v>1.427936673164368</v>
+        <v>1.432536244392395</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D190">
-        <v>0.2052420973777771</v>
+        <v>1.654969453811646</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D191">
-        <v>0.79569411277771</v>
+        <v>0.9731370806694031</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D192">
-        <v>12.04583358764648</v>
+        <v>11.02343654632568</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D193">
-        <v>4.623769760131836</v>
+        <v>5.226354598999023</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>1.012906908988953</v>
+        <v>0.4305745959281921</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D195">
-        <v>0.9555644989013672</v>
+        <v>0.9825944900512695</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D196">
-        <v>13.28573799133301</v>
+        <v>13.67720603942871</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D197">
-        <v>3.22973108291626</v>
+        <v>3.475298404693604</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D198">
-        <v>-0.03879895806312561</v>
+        <v>0.1266841292381287</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D199">
-        <v>5.276440620422363</v>
+        <v>3.858369112014771</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D200">
-        <v>0.1481035351753235</v>
+        <v>0.1479941606521606</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D201">
-        <v>-0.6417862176895142</v>
+        <v>-0.4150116443634033</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D202">
-        <v>-1.182793736457825</v>
+        <v>-0.5995235443115234</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>1.5</v>
       </c>
       <c r="D203">
-        <v>1.266768932342529</v>
+        <v>0.2941588163375854</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D204">
-        <v>2.979163646697998</v>
+        <v>4.778395652770996</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D205">
-        <v>2.110195159912109</v>
+        <v>2.642297983169556</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D206">
-        <v>10.33310127258301</v>
+        <v>11.46850490570068</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>-0.9976004362106323</v>
+        <v>-0.9837794303894043</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>3.5</v>
       </c>
       <c r="D208">
-        <v>3.552467107772827</v>
+        <v>3.433022260665894</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D209">
-        <v>-1.261398077011108</v>
+        <v>-0.4481679201126099</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D210">
-        <v>-1.86942720413208</v>
+        <v>-0.4462614059448242</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>3.5</v>
       </c>
       <c r="D211">
-        <v>1.403812527656555</v>
+        <v>1.479369640350342</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D212">
-        <v>2.092655897140503</v>
+        <v>2.313729763031006</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D213">
-        <v>4.157351970672607</v>
+        <v>3.851049184799194</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D214">
-        <v>-0.03751727938652039</v>
+        <v>0.2331108748912811</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D215">
-        <v>-1.661809086799622</v>
+        <v>-1.153567671775818</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D216">
-        <v>2.039883852005005</v>
+        <v>0.7740017771720886</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>-0.2349055707454681</v>
+        <v>-0.1355072259902954</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>-1.092068791389465</v>
+        <v>-1.038883328437805</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D219">
-        <v>1.280236601829529</v>
+        <v>0.9081847667694092</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>-1.5</v>
       </c>
       <c r="D220">
-        <v>-1.247355580329895</v>
+        <v>-0.9778423309326172</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D221">
-        <v>4.742878913879395</v>
+        <v>5.000927925109863</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D222">
-        <v>-1.313975811004639</v>
+        <v>-0.8747245073318481</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D223">
-        <v>-1.253804922103882</v>
+        <v>-2.379564046859741</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4704,7 +4704,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D224">
-        <v>-0.2260805666446686</v>
+        <v>-0.04256749153137207</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4718,7 +4718,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D225">
-        <v>-0.3974610865116119</v>
+        <v>-0.1510398387908936</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4732,7 +4732,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>4.533985614776611</v>
+        <v>4.489727020263672</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4746,7 +4746,7 @@
         <v>0.5</v>
       </c>
       <c r="D227">
-        <v>-1.026615500450134</v>
+        <v>-0.1402426362037659</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4760,7 +4760,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D228">
-        <v>-0.3335979878902435</v>
+        <v>0.2198495268821716</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4774,7 +4774,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D229">
-        <v>5.834535121917725</v>
+        <v>5.583345413208008</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>0.9709463119506836</v>
+        <v>0.9878243207931519</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4802,7 +4802,7 @@
         <v>-1</v>
       </c>
       <c r="D231">
-        <v>-1.022512912750244</v>
+        <v>-0.7546510696411133</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4816,7 +4816,7 @@
         <v>25</v>
       </c>
       <c r="D232">
-        <v>15.20822906494141</v>
+        <v>16.29979705810547</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4830,7 +4830,7 @@
         <v>0.5</v>
       </c>
       <c r="D233">
-        <v>2.877280473709106</v>
+        <v>2.076938390731812</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4844,7 +4844,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D234">
-        <v>1.241192817687988</v>
+        <v>0.8780272006988525</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4858,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>14.51201629638672</v>
+        <v>14.5614595413208</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4872,7 +4872,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D236">
-        <v>-4.531983375549316</v>
+        <v>-4.217012405395508</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4886,7 +4886,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D237">
-        <v>0.117594376206398</v>
+        <v>0.6780238151550293</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4900,7 +4900,7 @@
         <v>20.5</v>
       </c>
       <c r="D238">
-        <v>16.36643218994141</v>
+        <v>17.9372444152832</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4914,7 +4914,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D239">
-        <v>-0.08165529370307922</v>
+        <v>-0.121877908706665</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0.1271019279956818</v>
+        <v>0.1214532852172852</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4942,7 +4942,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D241">
-        <v>-0.3718921840190887</v>
+        <v>-0.08176374435424805</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4956,7 +4956,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D242">
-        <v>-1.507617235183716</v>
+        <v>-1.857026338577271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4970,7 +4970,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D243">
-        <v>0.2935086786746979</v>
+        <v>2.171123027801514</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4984,7 +4984,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D244">
-        <v>-0.3368418514728546</v>
+        <v>0.06238389015197754</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4998,7 +4998,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D245">
-        <v>1.228632688522339</v>
+        <v>1.718874335289001</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5012,7 +5012,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D246">
-        <v>-1.176678419113159</v>
+        <v>0.43849778175354</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5026,7 +5026,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D247">
-        <v>-1.219512462615967</v>
+        <v>-1.204757809638977</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5040,7 +5040,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D248">
-        <v>-0.1073883473873138</v>
+        <v>0.4012443721294403</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5054,7 +5054,7 @@
         <v>-22.60000038146973</v>
       </c>
       <c r="D249">
-        <v>-5.991443634033203</v>
+        <v>-6.657451629638672</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5068,7 +5068,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D250">
-        <v>-3.54196834564209</v>
+        <v>-3.483676671981812</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5082,7 +5082,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D251">
-        <v>4.579006195068359</v>
+        <v>4.651565551757812</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5096,7 +5096,7 @@
         <v>3.5</v>
       </c>
       <c r="D252">
-        <v>1.834735631942749</v>
+        <v>1.043349266052246</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5110,7 +5110,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D253">
-        <v>0.9548357725143433</v>
+        <v>1.252289891242981</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5124,7 +5124,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D254">
-        <v>-1.253630042076111</v>
+        <v>-1.347602605819702</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5138,7 +5138,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D255">
-        <v>4.799015045166016</v>
+        <v>3.633244514465332</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5152,7 +5152,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D256">
-        <v>-0.7360522747039795</v>
+        <v>-0.8509089946746826</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5166,7 +5166,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D257">
-        <v>-0.6938012838363647</v>
+        <v>-0.4391849040985107</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5180,7 +5180,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D258">
-        <v>0.07708664238452911</v>
+        <v>-0.4367213249206543</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5194,7 +5194,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>0.5729190707206726</v>
+        <v>0.822378933429718</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5208,7 +5208,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D260">
-        <v>-0.4394231736660004</v>
+        <v>-0.395177960395813</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5222,7 +5222,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D261">
-        <v>1.726642251014709</v>
+        <v>2.044897556304932</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5236,7 +5236,7 @@
         <v>-1</v>
       </c>
       <c r="D262">
-        <v>0.725746750831604</v>
+        <v>-0.04733180999755859</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5250,7 +5250,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D263">
-        <v>2.99661111831665</v>
+        <v>3.460397005081177</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5264,7 +5264,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D264">
-        <v>2.145722389221191</v>
+        <v>1.938056468963623</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5278,7 +5278,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D265">
-        <v>2.327533006668091</v>
+        <v>1.000930190086365</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5292,7 +5292,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D266">
-        <v>2.324838638305664</v>
+        <v>2.733695268630981</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5306,7 +5306,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D267">
-        <v>1.202577471733093</v>
+        <v>1.510818839073181</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5320,7 +5320,7 @@
         <v>37.20000076293945</v>
       </c>
       <c r="D268">
-        <v>22.65063858032227</v>
+        <v>22.58488464355469</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5334,7 +5334,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D269">
-        <v>-1.423084139823914</v>
+        <v>-1.690030336380005</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5348,7 +5348,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D270">
-        <v>2.256712198257446</v>
+        <v>3.839586496353149</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5362,7 +5362,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D271">
-        <v>3.02366304397583</v>
+        <v>2.673680543899536</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5376,7 +5376,7 @@
         <v>1.5</v>
       </c>
       <c r="D272">
-        <v>0.3528884649276733</v>
+        <v>0.1306134462356567</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5390,7 +5390,7 @@
         <v>-0.5</v>
       </c>
       <c r="D273">
-        <v>2.04847526550293</v>
+        <v>2.432034969329834</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5404,7 +5404,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D274">
-        <v>-5.622623443603516</v>
+        <v>-6.295700073242188</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5418,7 +5418,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-0.4354396760463715</v>
+        <v>-0.04535096883773804</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5432,7 +5432,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D276">
-        <v>6.454946994781494</v>
+        <v>5.202189445495605</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5446,7 +5446,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D277">
-        <v>1.515396356582642</v>
+        <v>1.290802240371704</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5460,7 +5460,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D278">
-        <v>5.534710884094238</v>
+        <v>5.273022651672363</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5474,7 +5474,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D279">
-        <v>-1.404135465621948</v>
+        <v>-1.335140943527222</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5488,7 +5488,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D280">
-        <v>1.839547514915466</v>
+        <v>2.140901565551758</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5502,7 +5502,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D281">
-        <v>11.01834869384766</v>
+        <v>12.52846622467041</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5516,7 +5516,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D282">
-        <v>11.83092784881592</v>
+        <v>10.17976093292236</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5530,7 +5530,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D283">
-        <v>1.079243898391724</v>
+        <v>1.348242044448853</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="D284">
-        <v>6.72627067565918</v>
+        <v>4.115890502929688</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5558,7 +5558,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>1.412753462791443</v>
+        <v>0.9927415251731873</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5572,7 +5572,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D286">
-        <v>0.6898248195648193</v>
+        <v>1.279232740402222</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5586,7 +5586,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D287">
-        <v>2.666825532913208</v>
+        <v>4.135294914245605</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5600,7 +5600,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D288">
-        <v>4.500170707702637</v>
+        <v>4.05703592300415</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5614,7 +5614,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D289">
-        <v>0.1985046565532684</v>
+        <v>1.705402851104736</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5628,7 +5628,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D290">
-        <v>7.001638412475586</v>
+        <v>7.439848899841309</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5642,7 +5642,7 @@
         <v>2.5</v>
       </c>
       <c r="D291">
-        <v>-1.155974268913269</v>
+        <v>-0.3581265211105347</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>3.171426296234131</v>
+        <v>1.523242235183716</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5670,7 +5670,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>-1.184186458587646</v>
+        <v>-0.7148661613464355</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5684,7 +5684,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D294">
-        <v>4.780489921569824</v>
+        <v>5.067571640014648</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5698,7 +5698,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D295">
-        <v>4.734839916229248</v>
+        <v>4.721879959106445</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5712,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="D296">
-        <v>1.175507783889771</v>
+        <v>1.174281239509583</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5726,7 +5726,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D297">
-        <v>-1.878121137619019</v>
+        <v>-1.787766695022583</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5740,7 +5740,7 @@
         <v>9.5</v>
       </c>
       <c r="D298">
-        <v>13.40038299560547</v>
+        <v>11.89737415313721</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5754,7 +5754,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D299">
-        <v>1.785241603851318</v>
+        <v>1.457995414733887</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5768,7 +5768,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D300">
-        <v>7.052758693695068</v>
+        <v>4.03421688079834</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5782,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="D301">
-        <v>1.326200008392334</v>
+        <v>2.481511354446411</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5796,7 +5796,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D302">
-        <v>1.856096029281616</v>
+        <v>2.492723226547241</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5810,7 +5810,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>1.36720860004425</v>
+        <v>-0.2122390270233154</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5824,7 +5824,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D304">
-        <v>0.4628432989120483</v>
+        <v>0.5577359199523926</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5838,7 +5838,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D305">
-        <v>-1.185639619827271</v>
+        <v>-0.6295719146728516</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5852,7 +5852,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>-2.601991176605225</v>
+        <v>-1.573146820068359</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5866,7 +5866,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D307">
-        <v>5.279901504516602</v>
+        <v>5.043866157531738</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5880,7 +5880,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D308">
-        <v>-0.3115414083003998</v>
+        <v>0.1148377060890198</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5894,7 +5894,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D309">
-        <v>-1.253707647323608</v>
+        <v>0.7612234950065613</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5908,7 +5908,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D310">
-        <v>-1.505447626113892</v>
+        <v>-1.320660352706909</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5922,7 +5922,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D311">
-        <v>1.533723831176758</v>
+        <v>1.495100498199463</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5936,7 +5936,7 @@
         <v>-2.5</v>
       </c>
       <c r="D312">
-        <v>-1.715716361999512</v>
+        <v>-1.056159138679504</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5950,7 +5950,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D313">
-        <v>2.310900211334229</v>
+        <v>1.573558688163757</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5964,7 +5964,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D314">
-        <v>-0.3968748152256012</v>
+        <v>-0.07766556739807129</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5978,7 +5978,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D315">
-        <v>1.381189346313477</v>
+        <v>3.168922901153564</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5992,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>-0.3168831169605255</v>
+        <v>-0.5998035669326782</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6006,7 +6006,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D317">
-        <v>0.7695629596710205</v>
+        <v>0.3256679475307465</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6020,7 +6020,7 @@
         <v>-8.5</v>
       </c>
       <c r="D318">
-        <v>-2.142667293548584</v>
+        <v>-1.856817007064819</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6034,7 +6034,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D319">
-        <v>4.188641548156738</v>
+        <v>4.101181030273438</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6048,7 +6048,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D320">
-        <v>6.47258996963501</v>
+        <v>6.35029411315918</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6062,7 +6062,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D321">
-        <v>9.570256233215332</v>
+        <v>9.758028984069824</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6076,7 +6076,7 @@
         <v>-4</v>
       </c>
       <c r="D322">
-        <v>1.762043476104736</v>
+        <v>1.772650957107544</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6090,7 +6090,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D323">
-        <v>2.241581201553345</v>
+        <v>3.188100576400757</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6104,7 +6104,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D324">
-        <v>9.123296737670898</v>
+        <v>9.031173706054688</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6118,7 +6118,7 @@
         <v>17.89999961853027</v>
       </c>
       <c r="D325">
-        <v>13.30173015594482</v>
+        <v>16.50223350524902</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6132,7 +6132,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D326">
-        <v>4.098376274108887</v>
+        <v>3.664618492126465</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6146,7 +6146,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D327">
-        <v>2.696973085403442</v>
+        <v>1.845852375030518</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6160,7 +6160,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D328">
-        <v>2.649763584136963</v>
+        <v>3.433960199356079</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6174,7 +6174,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D329">
-        <v>1.306514382362366</v>
+        <v>1.916454553604126</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6188,7 +6188,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D330">
-        <v>3.44099760055542</v>
+        <v>4.238443374633789</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6202,7 +6202,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D331">
-        <v>0.4382230639457703</v>
+        <v>1.264132738113403</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6216,7 +6216,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D332">
-        <v>-0.9212205410003662</v>
+        <v>-0.4742045402526855</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6230,7 +6230,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D333">
-        <v>3.270655632019043</v>
+        <v>2.801319360733032</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6244,7 +6244,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D334">
-        <v>-1.289964437484741</v>
+        <v>-1.473307371139526</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6258,7 +6258,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D335">
-        <v>-1.402750968933105</v>
+        <v>-1.018949151039124</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6272,7 +6272,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D336">
-        <v>-0.2246834337711334</v>
+        <v>0.4363664984703064</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6286,7 +6286,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D337">
-        <v>-0.0606253445148468</v>
+        <v>0.3112793266773224</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6300,7 +6300,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D338">
-        <v>-0.776556134223938</v>
+        <v>-0.5759060382843018</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6314,7 +6314,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D339">
-        <v>-0.6909233331680298</v>
+        <v>-0.6519887447357178</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6328,7 +6328,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D340">
-        <v>11.14670658111572</v>
+        <v>11.79019832611084</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6342,7 +6342,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>-0.1104947924613953</v>
+        <v>-0.1085076332092285</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6356,7 +6356,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D342">
-        <v>1.836184024810791</v>
+        <v>1.64478874206543</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6370,7 +6370,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D343">
-        <v>0.7900679111480713</v>
+        <v>0.1945869922637939</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6384,7 +6384,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D344">
-        <v>1.572038888931274</v>
+        <v>1.124201774597168</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6398,7 +6398,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D345">
-        <v>1.260882019996643</v>
+        <v>1.52131986618042</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6412,7 +6412,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D346">
-        <v>6.232397079467773</v>
+        <v>5.947413444519043</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6426,7 +6426,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D347">
-        <v>5.084635734558105</v>
+        <v>4.337995529174805</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6440,7 +6440,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D348">
-        <v>2.76043176651001</v>
+        <v>4.082098007202148</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6454,7 +6454,7 @@
         <v>-3</v>
       </c>
       <c r="D349">
-        <v>0.632146954536438</v>
+        <v>0.9782314896583557</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6468,7 +6468,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D350">
-        <v>1.778710126876831</v>
+        <v>1.484013080596924</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6482,7 +6482,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D351">
-        <v>-0.8646948337554932</v>
+        <v>-0.9687678813934326</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6496,7 +6496,7 @@
         <v>-0.5</v>
       </c>
       <c r="D352">
-        <v>0.1522942781448364</v>
+        <v>0.332196056842804</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6510,7 +6510,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D353">
-        <v>-2.726912498474121</v>
+        <v>-2.286954641342163</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6524,7 +6524,7 @@
         <v>3.5</v>
       </c>
       <c r="D354">
-        <v>2.491001844406128</v>
+        <v>2.615966796875</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6538,7 +6538,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D355">
-        <v>2.912497520446777</v>
+        <v>3.355327844619751</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6552,7 +6552,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D356">
-        <v>2.067039251327515</v>
+        <v>0.1837891340255737</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6566,7 +6566,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D357">
-        <v>6.119552612304688</v>
+        <v>4.597875595092773</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6580,7 +6580,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D358">
-        <v>-0.002298682928085327</v>
+        <v>-0.1897073984146118</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6594,7 +6594,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D359">
-        <v>-0.3148129880428314</v>
+        <v>0.4334742426872253</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6608,7 +6608,7 @@
         <v>-1</v>
       </c>
       <c r="D360">
-        <v>-1.068663597106934</v>
+        <v>-1.227490425109863</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6622,7 +6622,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D361">
-        <v>-1.192355871200562</v>
+        <v>-0.6247797012329102</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6636,7 +6636,7 @@
         <v>4.5</v>
       </c>
       <c r="D362">
-        <v>3.271215200424194</v>
+        <v>3.899185419082642</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6650,7 +6650,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D363">
-        <v>1.369020581245422</v>
+        <v>1.463375329971313</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6664,7 +6664,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D364">
-        <v>1.091701745986938</v>
+        <v>1.474125385284424</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6678,7 +6678,7 @@
         <v>35.09999847412109</v>
       </c>
       <c r="D365">
-        <v>23.41562652587891</v>
+        <v>24.50796318054199</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6692,7 +6692,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D366">
-        <v>0.5236691832542419</v>
+        <v>0.9350330829620361</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6706,7 +6706,7 @@
         <v>4</v>
       </c>
       <c r="D367">
-        <v>2.795177698135376</v>
+        <v>2.177579164505005</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6720,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>1.142343401908875</v>
+        <v>0.5051156282424927</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6734,7 +6734,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D369">
-        <v>4.397690296173096</v>
+        <v>3.521142721176147</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6748,7 +6748,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D370">
-        <v>2.070419311523438</v>
+        <v>2.907097101211548</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6762,7 +6762,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D371">
-        <v>-1.816273212432861</v>
+        <v>-0.4278802871704102</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6776,7 +6776,7 @@
         <v>-2.5</v>
       </c>
       <c r="D372">
-        <v>-1.484837412834167</v>
+        <v>-1.001069784164429</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6790,7 +6790,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D373">
-        <v>1.056684970855713</v>
+        <v>1.538027405738831</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6804,7 +6804,7 @@
         <v>-1.5</v>
       </c>
       <c r="D374">
-        <v>-4.213271141052246</v>
+        <v>-3.669296026229858</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6818,7 +6818,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D375">
-        <v>-5.210187911987305</v>
+        <v>-5.839967727661133</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6832,7 +6832,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D376">
-        <v>5.435096740722656</v>
+        <v>5.833601951599121</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6846,7 +6846,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D377">
-        <v>5.088937759399414</v>
+        <v>5.091699600219727</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6860,7 +6860,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D378">
-        <v>0.3657507002353668</v>
+        <v>0.3840307891368866</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6874,7 +6874,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D379">
-        <v>-0.397127777338028</v>
+        <v>-0.1042571067810059</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6888,7 +6888,7 @@
         <v>2.5</v>
       </c>
       <c r="D380">
-        <v>-1.193644285202026</v>
+        <v>-0.7762367725372314</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6902,7 +6902,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D381">
-        <v>2.565101623535156</v>
+        <v>2.171215534210205</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6916,7 +6916,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D382">
-        <v>2.792992115020752</v>
+        <v>5.640354156494141</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6930,7 +6930,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D383">
-        <v>2.182254791259766</v>
+        <v>2.995844841003418</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6944,7 +6944,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D384">
-        <v>-0.01381343603134155</v>
+        <v>-0.1149912476539612</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6958,7 +6958,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D385">
-        <v>22.6805305480957</v>
+        <v>20.85043144226074</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6972,7 +6972,7 @@
         <v>4.5</v>
       </c>
       <c r="D386">
-        <v>2.688105583190918</v>
+        <v>2.955250978469849</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6986,7 +6986,7 @@
         <v>8</v>
       </c>
       <c r="D387">
-        <v>5.202262878417969</v>
+        <v>5.447223663330078</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7000,7 +7000,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D388">
-        <v>2.008721828460693</v>
+        <v>1.332604169845581</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7014,7 +7014,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D389">
-        <v>0.5786377787590027</v>
+        <v>0.1480545997619629</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7028,7 +7028,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D390">
-        <v>-0.5088919401168823</v>
+        <v>-0.2504653334617615</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7042,7 +7042,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D391">
-        <v>6.42021656036377</v>
+        <v>6.444748878479004</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7056,7 +7056,7 @@
         <v>19</v>
       </c>
       <c r="D392">
-        <v>17.25626373291016</v>
+        <v>16.30899047851562</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7070,7 +7070,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D393">
-        <v>1.509822368621826</v>
+        <v>2.716087102890015</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7084,7 +7084,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D394">
-        <v>1.652700424194336</v>
+        <v>1.769473552703857</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7098,7 +7098,7 @@
         <v>12</v>
       </c>
       <c r="D395">
-        <v>5.536538124084473</v>
+        <v>5.54624080657959</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7112,7 +7112,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D396">
-        <v>-3.014462471008301</v>
+        <v>-2.372927904129028</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7126,7 +7126,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D397">
-        <v>7.154829025268555</v>
+        <v>5.360856056213379</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7140,7 +7140,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D398">
-        <v>6.911418914794922</v>
+        <v>5.577532768249512</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7154,7 +7154,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D399">
-        <v>-1.129338979721069</v>
+        <v>-0.5657460689544678</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7168,7 +7168,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D400">
-        <v>-0.237630695104599</v>
+        <v>-0.345966100692749</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7182,7 +7182,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D401">
-        <v>0.7747875452041626</v>
+        <v>1.335669875144958</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7196,7 +7196,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D402">
-        <v>6.1137375831604</v>
+        <v>5.837709426879883</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7210,7 +7210,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D403">
-        <v>0.4215939044952393</v>
+        <v>0.6812264919281006</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7224,7 +7224,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D404">
-        <v>3.281587362289429</v>
+        <v>3.929631233215332</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7238,7 +7238,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D405">
-        <v>0.6828900575637817</v>
+        <v>0.5084958076477051</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7252,7 +7252,7 @@
         <v>-3</v>
       </c>
       <c r="D406">
-        <v>-1.494182705879211</v>
+        <v>-1.175974488258362</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7266,7 +7266,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D407">
-        <v>-1.560670852661133</v>
+        <v>-1.448068857192993</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7280,7 +7280,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D408">
-        <v>-0.6722960472106934</v>
+        <v>-0.04497718811035156</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7294,7 +7294,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D409">
-        <v>8.899620056152344</v>
+        <v>10.12672138214111</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7308,7 +7308,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D410">
-        <v>0.3576343953609467</v>
+        <v>0.4060033559799194</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7322,7 +7322,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D411">
-        <v>-1.380417108535767</v>
+        <v>-1.386603593826294</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7336,7 +7336,7 @@
         <v>-1.5</v>
       </c>
       <c r="D412">
-        <v>-1.150488018989563</v>
+        <v>-0.5414770841598511</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7350,7 +7350,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D413">
-        <v>0.5367152690887451</v>
+        <v>1.602530717849731</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7364,7 +7364,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D414">
-        <v>4.147270679473877</v>
+        <v>4.287256240844727</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7378,7 +7378,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D415">
-        <v>6.49165153503418</v>
+        <v>5.837339401245117</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7392,7 +7392,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D416">
-        <v>1.098690867424011</v>
+        <v>0.9409401416778564</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7406,7 +7406,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D417">
-        <v>5.807607173919678</v>
+        <v>4.239229202270508</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7420,7 +7420,7 @@
         <v>5</v>
       </c>
       <c r="D418">
-        <v>2.68163800239563</v>
+        <v>4.306944847106934</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7434,7 +7434,7 @@
         <v>13</v>
       </c>
       <c r="D419">
-        <v>9.322564125061035</v>
+        <v>9.844019889831543</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7448,7 +7448,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D420">
-        <v>1.591099619865417</v>
+        <v>0.865510880947113</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7462,7 +7462,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D421">
-        <v>-5.11652660369873</v>
+        <v>-4.507695198059082</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7476,7 +7476,7 @@
         <v>22</v>
       </c>
       <c r="D422">
-        <v>16.90215301513672</v>
+        <v>15.74266815185547</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7490,7 +7490,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D423">
-        <v>0.354792982339859</v>
+        <v>0.8348703980445862</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7504,7 +7504,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D424">
-        <v>-0.150670200586319</v>
+        <v>-0.4998133182525635</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7518,7 +7518,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D425">
-        <v>6.913370609283447</v>
+        <v>6.421601295471191</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7532,7 +7532,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D426">
-        <v>3.741884469985962</v>
+        <v>3.757235288619995</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7546,7 +7546,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D427">
-        <v>0.1426646560430527</v>
+        <v>-0.01427674293518066</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7560,7 +7560,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D428">
-        <v>1.543572783470154</v>
+        <v>2.212889909744263</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7574,7 +7574,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D429">
-        <v>5.327220916748047</v>
+        <v>5.59035587310791</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7588,7 +7588,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D430">
-        <v>4.736563205718994</v>
+        <v>5.066681861877441</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7602,7 +7602,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D431">
-        <v>7.00446891784668</v>
+        <v>6.639881134033203</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7616,7 +7616,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>-0.419706791639328</v>
+        <v>0.08961009979248047</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7630,7 +7630,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D433">
-        <v>-1.757059097290039</v>
+        <v>-0.8230187892913818</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7644,7 +7644,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>0.1101579517126083</v>
+        <v>-0.05357599258422852</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7658,7 +7658,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D435">
-        <v>2.593002796173096</v>
+        <v>2.647186756134033</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7672,7 +7672,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D436">
-        <v>2.677150011062622</v>
+        <v>2.910573959350586</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7686,7 +7686,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D437">
-        <v>0.4060215055942535</v>
+        <v>1.482743144035339</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7700,7 +7700,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D438">
-        <v>8.411665916442871</v>
+        <v>10.65530872344971</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7714,7 +7714,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D439">
-        <v>4.882922649383545</v>
+        <v>3.336511850357056</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="D440">
-        <v>-0.6945040225982666</v>
+        <v>0.5831773281097412</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="D441">
-        <v>4.331794738769531</v>
+        <v>3.912910461425781</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>1.281830430030823</v>
+        <v>3.380103826522827</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7770,7 +7770,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D443">
-        <v>-0.4953896701335907</v>
+        <v>0.5050211548805237</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7784,7 +7784,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D444">
-        <v>2.389849662780762</v>
+        <v>2.148468017578125</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="D445">
-        <v>2.092695474624634</v>
+        <v>2.163659572601318</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7812,7 +7812,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D446">
-        <v>4.919431686401367</v>
+        <v>2.595168828964233</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7826,7 +7826,7 @@
         <v>-3</v>
       </c>
       <c r="D447">
-        <v>2.531903743743896</v>
+        <v>1.639734506607056</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7840,7 +7840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D448">
-        <v>0.6142663955688477</v>
+        <v>0.2890084087848663</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7854,7 +7854,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D449">
-        <v>-2.123888969421387</v>
+        <v>-3.41134238243103</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7868,7 +7868,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D450">
-        <v>2.691584348678589</v>
+        <v>2.546341419219971</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7882,7 +7882,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D451">
-        <v>2.917962074279785</v>
+        <v>3.155005216598511</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7896,7 +7896,7 @@
         <v>-2</v>
       </c>
       <c r="D452">
-        <v>0.1882055848836899</v>
+        <v>0.09849822521209717</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7910,7 +7910,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D453">
-        <v>3.923494577407837</v>
+        <v>2.900175809860229</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="D454">
-        <v>1.203095197677612</v>
+        <v>0.7131268978118896</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7938,7 +7938,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D455">
-        <v>-1.402750492095947</v>
+        <v>-1.318347692489624</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7952,7 +7952,7 @@
         <v>13</v>
       </c>
       <c r="D456">
-        <v>11.70328712463379</v>
+        <v>11.87530040740967</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7966,7 +7966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D457">
-        <v>4.183955192565918</v>
+        <v>4.208525657653809</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7980,7 +7980,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D458">
-        <v>-1.424753546714783</v>
+        <v>-0.9267287254333496</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7994,7 +7994,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D459">
-        <v>-2.28260350227356</v>
+        <v>-1.819906949996948</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8008,7 +8008,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D460">
-        <v>1.669283390045166</v>
+        <v>1.594790577888489</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8022,7 +8022,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D461">
-        <v>3.51311731338501</v>
+        <v>1.98452353477478</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8036,7 +8036,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D462">
-        <v>0.02366781234741211</v>
+        <v>0.3703007996082306</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8050,7 +8050,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D463">
-        <v>-0.2459870278835297</v>
+        <v>-0.1570050716400146</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8064,7 +8064,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>3.64590859413147</v>
+        <v>3.637375831604004</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8078,7 +8078,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D465">
-        <v>4.192936897277832</v>
+        <v>3.381828546524048</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8092,7 +8092,7 @@
         <v>0.5</v>
       </c>
       <c r="D466">
-        <v>1.371455192565918</v>
+        <v>2.328201770782471</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8106,7 +8106,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D467">
-        <v>-1.135413646697998</v>
+        <v>-0.802318811416626</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8120,7 +8120,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D468">
-        <v>0.1160432398319244</v>
+        <v>0.1140744686126709</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8134,7 +8134,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D469">
-        <v>1.788691639900208</v>
+        <v>1.746783137321472</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8148,7 +8148,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D470">
-        <v>1.893944978713989</v>
+        <v>3.684084177017212</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8162,7 +8162,7 @@
         <v>-3.5</v>
       </c>
       <c r="D471">
-        <v>-0.6300740242004395</v>
+        <v>-1.029447317123413</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8176,7 +8176,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>-0.088910311460495</v>
+        <v>0.05347424745559692</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8190,7 +8190,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D473">
-        <v>0.0446033775806427</v>
+        <v>0.3757718801498413</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8204,7 +8204,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D474">
-        <v>4.363669395446777</v>
+        <v>4.620159149169922</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8218,7 +8218,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D475">
-        <v>5.641090393066406</v>
+        <v>6.484735488891602</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8232,7 +8232,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D476">
-        <v>-4.75616455078125</v>
+        <v>-2.562359094619751</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8246,7 +8246,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D477">
-        <v>-1.086699247360229</v>
+        <v>-0.6387462615966797</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8260,7 +8260,7 @@
         <v>2.5</v>
       </c>
       <c r="D478">
-        <v>-1.386639475822449</v>
+        <v>-1.717490434646606</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8274,7 +8274,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D479">
-        <v>-0.5509846210479736</v>
+        <v>-0.2575082778930664</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8288,7 +8288,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D480">
-        <v>0.4049423933029175</v>
+        <v>0.2302577793598175</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8302,7 +8302,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D481">
-        <v>-0.3942640721797943</v>
+        <v>-0.1984059810638428</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8316,7 +8316,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D482">
-        <v>1.576480269432068</v>
+        <v>2.661059379577637</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8330,7 +8330,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D483">
-        <v>1.501334547996521</v>
+        <v>1.106421709060669</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8344,7 +8344,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D484">
-        <v>0.8972257375717163</v>
+        <v>3.050633192062378</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8358,7 +8358,7 @@
         <v>36.09999847412109</v>
       </c>
       <c r="D485">
-        <v>25.63993644714355</v>
+        <v>24.3817310333252</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8372,7 +8372,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D486">
-        <v>-0.1496032476425171</v>
+        <v>0.02669060230255127</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8386,7 +8386,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D487">
-        <v>3.857335090637207</v>
+        <v>3.976297378540039</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8400,7 +8400,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D488">
-        <v>-1.701653480529785</v>
+        <v>-1.153619050979614</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8414,7 +8414,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D489">
-        <v>-1.965229988098145</v>
+        <v>-1.795574903488159</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8428,7 +8428,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D490">
-        <v>-3.825437545776367</v>
+        <v>-4.001497268676758</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8442,7 +8442,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D491">
-        <v>0.7807904481887817</v>
+        <v>0.07307565212249756</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8456,7 +8456,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D492">
-        <v>3.768787622451782</v>
+        <v>5.086739540100098</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8470,7 +8470,7 @@
         <v>-3</v>
       </c>
       <c r="D493">
-        <v>-0.4081608951091766</v>
+        <v>-0.09821999073028564</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8484,7 +8484,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D494">
-        <v>3.054149627685547</v>
+        <v>2.796859741210938</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8498,7 +8498,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D495">
-        <v>-1.174810409545898</v>
+        <v>-0.8086023330688477</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8512,7 +8512,7 @@
         <v>0.5</v>
       </c>
       <c r="D496">
-        <v>0.1322864443063736</v>
+        <v>0.4623502492904663</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8526,7 +8526,7 @@
         <v>-2</v>
       </c>
       <c r="D497">
-        <v>-0.1339785754680634</v>
+        <v>0.3751535713672638</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8540,7 +8540,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D498">
-        <v>1.252715706825256</v>
+        <v>2.026671409606934</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8554,7 +8554,7 @@
         <v>13</v>
       </c>
       <c r="D499">
-        <v>2.785619020462036</v>
+        <v>0.1749882698059082</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8568,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>2.482448577880859</v>
+        <v>2.051260948181152</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8582,7 +8582,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D501">
-        <v>-1.462725043296814</v>
+        <v>-1.041477680206299</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8596,7 +8596,7 @@
         <v>8.5</v>
       </c>
       <c r="D502">
-        <v>7.1513671875</v>
+        <v>6.800230026245117</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8610,7 +8610,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D503">
-        <v>2.181401491165161</v>
+        <v>2.903491735458374</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8624,7 +8624,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D504">
-        <v>4.478150367736816</v>
+        <v>4.844327926635742</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8638,7 +8638,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D505">
-        <v>2.629551410675049</v>
+        <v>2.076344728469849</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8652,7 +8652,7 @@
         <v>6.5</v>
       </c>
       <c r="D506">
-        <v>4.113780975341797</v>
+        <v>1.939001560211182</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8666,7 +8666,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D507">
-        <v>1.639174222946167</v>
+        <v>1.328255176544189</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8680,7 +8680,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D508">
-        <v>3.18712043762207</v>
+        <v>2.273551940917969</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8694,7 +8694,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D509">
-        <v>3.537820816040039</v>
+        <v>2.705773591995239</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8708,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="D510">
-        <v>2.748093128204346</v>
+        <v>1.563696384429932</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8722,7 +8722,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D511">
-        <v>-3.126165866851807</v>
+        <v>-3.863956212997437</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8736,7 +8736,7 @@
         <v>32.5</v>
       </c>
       <c r="D512">
-        <v>18.39368057250977</v>
+        <v>17.52928924560547</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8750,7 +8750,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D513">
-        <v>1.961098909378052</v>
+        <v>3.728341102600098</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8764,7 +8764,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D514">
-        <v>-1.557598829269409</v>
+        <v>-0.7042689323425293</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8778,7 +8778,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>-1.984740257263184</v>
+        <v>-0.751947283744812</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8792,7 +8792,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D516">
-        <v>1.904553174972534</v>
+        <v>0.3340097069740295</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8806,7 +8806,7 @@
         <v>-1.5</v>
       </c>
       <c r="D517">
-        <v>0.3767046630382538</v>
+        <v>1.861282706260681</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8820,7 +8820,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D518">
-        <v>-1.657201409339905</v>
+        <v>-2.287521123886108</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8834,7 +8834,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D519">
-        <v>-5.179470062255859</v>
+        <v>-6.305488586425781</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8848,7 +8848,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D520">
-        <v>3.266667366027832</v>
+        <v>2.368766784667969</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8862,7 +8862,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D521">
-        <v>10.00226974487305</v>
+        <v>10.18573570251465</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8876,7 +8876,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D522">
-        <v>-0.2316373288631439</v>
+        <v>-0.09817785024642944</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8890,7 +8890,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D523">
-        <v>7.63097095489502</v>
+        <v>7.160441398620605</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8904,7 +8904,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D524">
-        <v>-0.3482711017131805</v>
+        <v>0.3249039947986603</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8918,7 +8918,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D525">
-        <v>11.80893135070801</v>
+        <v>15.15763187408447</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8932,7 +8932,7 @@
         <v>-3</v>
       </c>
       <c r="D526">
-        <v>-1.87723183631897</v>
+        <v>-2.002489328384399</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8946,7 +8946,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D527">
-        <v>4.758425235748291</v>
+        <v>3.489542484283447</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8960,7 +8960,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D528">
-        <v>3.09727668762207</v>
+        <v>3.773601293563843</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8974,7 +8974,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D529">
-        <v>-0.0581011176109314</v>
+        <v>0.4599520862102509</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8988,7 +8988,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D530">
-        <v>-1.526384353637695</v>
+        <v>-0.9614354372024536</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9002,7 +9002,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D531">
-        <v>-3.138932704925537</v>
+        <v>-2.708023548126221</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9016,7 +9016,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D532">
-        <v>-0.1808759272098541</v>
+        <v>0.316770613193512</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9030,7 +9030,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D533">
-        <v>-0.7966420650482178</v>
+        <v>-1.16935920715332</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9044,7 +9044,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D534">
-        <v>0.6126391887664795</v>
+        <v>0.3738706707954407</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9058,7 +9058,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D535">
-        <v>6.505693912506104</v>
+        <v>5.856607437133789</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9072,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="D536">
-        <v>15.12896156311035</v>
+        <v>16.12825775146484</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9086,7 +9086,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D537">
-        <v>5.455733776092529</v>
+        <v>5.825471878051758</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9100,7 +9100,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D538">
-        <v>1.461134314537048</v>
+        <v>1.150834083557129</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9114,7 +9114,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D539">
-        <v>10.43529796600342</v>
+        <v>10.92871379852295</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9128,7 +9128,7 @@
         <v>27.5</v>
       </c>
       <c r="D540">
-        <v>12.81535625457764</v>
+        <v>12.30913066864014</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9142,7 +9142,7 @@
         <v>6</v>
       </c>
       <c r="D541">
-        <v>-0.8285707235336304</v>
+        <v>0.4606491923332214</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9156,7 +9156,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D542">
-        <v>2.242153882980347</v>
+        <v>4.133326530456543</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9170,7 +9170,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D543">
-        <v>1.256135940551758</v>
+        <v>-0.1749398708343506</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9184,7 +9184,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D544">
-        <v>1.266720294952393</v>
+        <v>1.6249098777771</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9198,7 +9198,7 @@
         <v>1.5</v>
       </c>
       <c r="D545">
-        <v>-1.407031536102295</v>
+        <v>-1.274833917617798</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9212,7 +9212,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D546">
-        <v>-0.8043520450592041</v>
+        <v>-0.8484686613082886</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9226,7 +9226,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D547">
-        <v>7.330542087554932</v>
+        <v>7.552786827087402</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9240,7 +9240,7 @@
         <v>-8.600000381469727</v>
       </c>
       <c r="D548">
-        <v>-2.1670823097229</v>
+        <v>-2.073296308517456</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9254,7 +9254,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D549">
-        <v>-0.2205069363117218</v>
+        <v>2.023931503295898</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9268,7 +9268,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D550">
-        <v>2.835989475250244</v>
+        <v>3.464026212692261</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9282,7 +9282,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D551">
-        <v>4.172118186950684</v>
+        <v>4.838229179382324</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9296,7 +9296,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D552">
-        <v>6.539676666259766</v>
+        <v>5.834553718566895</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9310,7 +9310,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D553">
-        <v>-1.02822470664978</v>
+        <v>-0.1812419891357422</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9324,7 +9324,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D554">
-        <v>0.1853393912315369</v>
+        <v>-0.2622565031051636</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9338,7 +9338,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D555">
-        <v>-0.3212915360927582</v>
+        <v>0.185739278793335</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9352,7 +9352,7 @@
         <v>2</v>
       </c>
       <c r="D556">
-        <v>2.411421298980713</v>
+        <v>1.493709564208984</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9366,7 +9366,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D557">
-        <v>-1.060550451278687</v>
+        <v>-1.179481744766235</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9380,7 +9380,7 @@
         <v>6</v>
       </c>
       <c r="D558">
-        <v>5.220485687255859</v>
+        <v>4.632786750793457</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9394,7 +9394,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D559">
-        <v>4.02414608001709</v>
+        <v>2.93852710723877</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9408,7 +9408,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D560">
-        <v>-0.4049040973186493</v>
+        <v>-0.6074895858764648</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9422,7 +9422,7 @@
         <v>-4</v>
       </c>
       <c r="D561">
-        <v>-0.1565479934215546</v>
+        <v>0.1422568559646606</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9436,7 +9436,7 @@
         <v>-2.5</v>
       </c>
       <c r="D562">
-        <v>-2.058217763900757</v>
+        <v>-1.502840995788574</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9450,7 +9450,7 @@
         <v>1.5</v>
       </c>
       <c r="D563">
-        <v>1.112723469734192</v>
+        <v>1.025946855545044</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9464,7 +9464,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D564">
-        <v>-1.926641225814819</v>
+        <v>-0.7170131206512451</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9478,7 +9478,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D565">
-        <v>0.8482201099395752</v>
+        <v>0.2778359055519104</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9492,7 +9492,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D566">
-        <v>-0.02488440275192261</v>
+        <v>1.674274444580078</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9506,7 +9506,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D567">
-        <v>6.613492965698242</v>
+        <v>5.862333297729492</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9520,7 +9520,7 @@
         <v>5.5</v>
       </c>
       <c r="D568">
-        <v>5.892623901367188</v>
+        <v>4.883484840393066</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9534,7 +9534,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D569">
-        <v>-1.704246044158936</v>
+        <v>0.1832791566848755</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9548,7 +9548,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D570">
-        <v>2.593662261962891</v>
+        <v>3.044664621353149</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9562,7 +9562,7 @@
         <v>4</v>
       </c>
       <c r="D571">
-        <v>1.758926510810852</v>
+        <v>2.460548639297485</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9576,7 +9576,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D572">
-        <v>-0.5345675945281982</v>
+        <v>-0.4919290542602539</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9590,7 +9590,7 @@
         <v>-1.5</v>
       </c>
       <c r="D573">
-        <v>4.641605377197266</v>
+        <v>4.359899520874023</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9604,7 +9604,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D574">
-        <v>5.07777214050293</v>
+        <v>4.395696640014648</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="D575">
-        <v>-0.2985292375087738</v>
+        <v>-0.05638158321380615</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9632,7 +9632,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D576">
-        <v>2.271361112594604</v>
+        <v>2.034755229949951</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9646,7 +9646,7 @@
         <v>-0.5</v>
       </c>
       <c r="D577">
-        <v>-0.4831114709377289</v>
+        <v>-0.3668934106826782</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9660,7 +9660,7 @@
         <v>0.5</v>
       </c>
       <c r="D578">
-        <v>2.329310178756714</v>
+        <v>2.647533893585205</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9674,7 +9674,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>2.937390565872192</v>
+        <v>3.502816677093506</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9688,7 +9688,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D580">
-        <v>15.68310737609863</v>
+        <v>15.23458480834961</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9702,7 +9702,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D581">
-        <v>2.005068778991699</v>
+        <v>0.8417818546295166</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9716,7 +9716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D582">
-        <v>0.1854203343391418</v>
+        <v>1.722010493278503</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9730,7 +9730,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D583">
-        <v>-0.02521911263465881</v>
+        <v>-0.1931090354919434</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="D584">
-        <v>0.5356351733207703</v>
+        <v>1.301143884658813</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9758,7 +9758,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D585">
-        <v>-0.6439239978790283</v>
+        <v>-0.4244704246520996</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9772,7 +9772,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D586">
-        <v>5.313087940216064</v>
+        <v>5.794549942016602</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9786,7 +9786,7 @@
         <v>2</v>
       </c>
       <c r="D587">
-        <v>2.394686698913574</v>
+        <v>2.327070474624634</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9800,7 +9800,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D588">
-        <v>-1.734956741333008</v>
+        <v>-2.365745067596436</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9814,7 +9814,7 @@
         <v>10</v>
       </c>
       <c r="D589">
-        <v>4.776286602020264</v>
+        <v>4.16313648223877</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9828,7 +9828,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D590">
-        <v>2.151346445083618</v>
+        <v>1.88303542137146</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9842,7 +9842,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D591">
-        <v>1.247540354728699</v>
+        <v>1.15840482711792</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9856,7 +9856,7 @@
         <v>34.59999847412109</v>
       </c>
       <c r="D592">
-        <v>27.68247032165527</v>
+        <v>28.65887641906738</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9870,7 +9870,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D593">
-        <v>-5.037174224853516</v>
+        <v>-6.020078659057617</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9884,7 +9884,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D594">
-        <v>-0.4369965493679047</v>
+        <v>-0.2257035970687866</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9898,7 +9898,7 @@
         <v>0.5</v>
       </c>
       <c r="D595">
-        <v>1.511951684951782</v>
+        <v>1.353102922439575</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9912,7 +9912,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D596">
-        <v>-2.197067737579346</v>
+        <v>-1.813446283340454</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9926,7 +9926,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D597">
-        <v>-1.063376188278198</v>
+        <v>-0.1511704921722412</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9940,7 +9940,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D598">
-        <v>3.740349292755127</v>
+        <v>3.284641265869141</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9954,7 +9954,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D599">
-        <v>4.411011695861816</v>
+        <v>4.38930606842041</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9968,7 +9968,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D600">
-        <v>-1.522791028022766</v>
+        <v>-0.9478219747543335</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9982,7 +9982,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D601">
-        <v>-5.293948173522949</v>
+        <v>-2.958072900772095</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -9996,7 +9996,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D602">
-        <v>1.605924367904663</v>
+        <v>2.406256198883057</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10010,7 +10010,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D603">
-        <v>-0.5803686380386353</v>
+        <v>0.01778161525726318</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="D604">
-        <v>-0.01317319273948669</v>
+        <v>0.1752165555953979</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10038,7 +10038,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D605">
-        <v>4.467010498046875</v>
+        <v>5.28361988067627</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10052,7 +10052,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D606">
-        <v>-0.2254928052425385</v>
+        <v>-0.267335832118988</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10066,7 +10066,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D607">
-        <v>2.365625381469727</v>
+        <v>0.05748385190963745</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10080,7 +10080,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D608">
-        <v>5.818601131439209</v>
+        <v>4.150439262390137</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10094,7 +10094,7 @@
         <v>-0.5</v>
       </c>
       <c r="D609">
-        <v>-0.4202177226543427</v>
+        <v>-0.1590202450752258</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10108,7 +10108,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D610">
-        <v>2.830552101135254</v>
+        <v>3.507182121276855</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10122,7 +10122,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D611">
-        <v>4.191897392272949</v>
+        <v>4.152610301971436</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10136,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="D612">
-        <v>1.131363868713379</v>
+        <v>0.4916237890720367</v>
       </c>
     </row>
   </sheetData>
